--- a/First semester/Intelligent System Control/1. Slides/2.Terminology and Objectives of Control/members and topic of your group.xlsx
+++ b/First semester/Intelligent System Control/1. Slides/2.Terminology and Objectives of Control/members and topic of your group.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\个人资料\BJV_Repository\First semester\Intelligent System Control\1. Slides\2.Terminology and Objectives of Control\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549F0E83-1B62-4BA5-94B4-67B1015A2DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr fullCalcOnLoad="false"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>member names</t>
   </si>
@@ -26,61 +35,31 @@
     <t>topic</t>
   </si>
   <si>
-    <t>ZhouXiaoyao  GaoXujie</t>
-  </si>
-  <si>
     <t>Adaptive Traffic Signal Control for Smart Cities using Real-Time Sensor Data</t>
   </si>
   <si>
-    <t>LiuZengrui NieJialin</t>
-  </si>
-  <si>
     <t>Digital Twin Modelling of Adaptive Signal Processing for Smart Transportation Systems</t>
   </si>
   <si>
-    <t>SuYufei  ZhengHuizhong</t>
-  </si>
-  <si>
     <t>Air Pollution Monitoring and Forecasting using DSP and State-Space Models</t>
   </si>
   <si>
-    <t>FengCong  ZhouZishan</t>
-  </si>
-  <si>
     <t>IoT-Enabled Precision Irrigation for Smart Agriculture</t>
   </si>
   <si>
-    <t>LvMingchenSunLiang</t>
-  </si>
-  <si>
     <t>Environmental Disaster Early Warning via Sensor Network Simulation</t>
   </si>
   <si>
-    <t>Longzequan  Huijiarui</t>
-  </si>
-  <si>
     <t>Energy-Aware Robust Control for Electric Vehicle Charging Networks using Smart Grids</t>
   </si>
   <si>
-    <t>ZhaoWeiming  SunYuteng</t>
-  </si>
-  <si>
     <t>AI-Powered Adaptive Beamforming for Massive MIMO Systems</t>
   </si>
   <si>
-    <t>Zhanghanlin Zhangzunlu</t>
-  </si>
-  <si>
     <t>Edge-Enabled Predictive Control for IoT-Based Health Monitoring Systems</t>
   </si>
   <si>
-    <t>BaYuxi ZhangQianqian</t>
-  </si>
-  <si>
     <t>Smart Waste Collection：Optimal Routing using Control and Signal Data</t>
-  </si>
-  <si>
-    <t>jinzizhao liluyao</t>
   </si>
   <si>
     <t xml:space="preserve">Design and Simulation of Optimal PI Controllers for OFDM-based Communication Systems
@@ -90,215 +69,182 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="300" formatCode="General"/>
-    <numFmt numFmtId="301" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="302" formatCode="0%"/>
-    <numFmt numFmtId="303" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="304" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="305" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="23">
+    <font>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF175CEB"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <u/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <b val="true"/>
-    </font>
-    <font>
       <name val="Aptos"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+    </font>
+    <font>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <i val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="3"/>
-      <sz val="18"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="major"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="-122"/>
-      <family val="0"/>
-      <b val="true"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -319,13 +265,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39998"/>
+        <fgColor theme="8" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -343,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39998"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -361,7 +307,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39998"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,7 +319,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,7 +331,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999"/>
+        <fgColor theme="4" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -415,7 +361,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39998"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,19 +373,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,31 +397,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39998"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,13 +433,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59996337778862885"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,18 +460,13 @@
       <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -540,34 +481,25 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39998"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -582,6 +514,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -596,6 +529,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -610,179 +544,155 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.49998"/>
+        <color theme="4" tint="0.49995422223578601"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
-    <xf numFmtId="300" fontId="6" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="300" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="11" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="16" fillId="12" borderId="6" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="301" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="17" fillId="14" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="15" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="302" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="18" fillId="16" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="19" fillId="17" borderId="7" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="20" fillId="18" borderId="8" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="10" fillId="19" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="303" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="304" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="20" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="21" fillId="2" borderId="9" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="305" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="10" fillId="21" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="22" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="23" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="23" fillId="18" borderId="7" xfId="0" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="24" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="10" fillId="25" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="26" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="27" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="28" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="29" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="30" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="10" fillId="31" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="32" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="25" fillId="2" borderId="10" xfId="0" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="300" fontId="9" fillId="33" borderId="1" xfId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="6" fillId="0" borderId="1" xfId="0" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="300" fontId="6" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1"/>
-    <cellStyle name="标题 1" xfId="2"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="3"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="4"/>
-    <cellStyle name="注释" xfId="5"/>
-    <cellStyle name="强调文字颜色 6" xfId="6"/>
-    <cellStyle name="警告文本" xfId="7"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="8"/>
-    <cellStyle name="解释性文本" xfId="9"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="10"/>
-    <cellStyle name="标题 3" xfId="11"/>
-    <cellStyle name="标题" xfId="12"/>
-    <cellStyle name="链接单元格" xfId="13"/>
-    <cellStyle name="强调文字颜色 4" xfId="14"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="15"/>
-    <cellStyle name="检查单元格" xfId="16"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="17"/>
-    <cellStyle name="Currency" xfId="18" builtinId="4"/>
-    <cellStyle name="差" xfId="19"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="20"/>
-    <cellStyle name="Percent" xfId="21" builtinId="5"/>
-    <cellStyle name="适中" xfId="22"/>
-    <cellStyle name="输入" xfId="23"/>
-    <cellStyle name="输出" xfId="24"/>
-    <cellStyle name="强调文字颜色 1" xfId="25"/>
-    <cellStyle name="Comma" xfId="26" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="27" builtinId="6"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <cellStyle name="汇总" xfId="29"/>
-    <cellStyle name="Currency [0]" xfId="30" builtinId="7"/>
-    <cellStyle name="强调文字颜色 2" xfId="31"/>
-    <cellStyle name="Hyperlink" xfId="32" builtinId="8"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="33"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <cellStyle name="计算" xfId="35"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="37"/>
-    <cellStyle name="标题 4" xfId="38"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="39"/>
-    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="46"/>
-    <cellStyle name="标题 2" xfId="47"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="48"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - 强调文字颜色 1" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="35" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="39" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="19" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="30" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="36" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="41" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="24" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="37" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="标题" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="标题 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="标题 2" xfId="40" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="标题 3" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="标题 4" xfId="32" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="差" xfId="18" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="汇总" xfId="25" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="计算" xfId="29" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="检查单元格" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="解释性文本" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="警告文本" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="链接单元格" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="强调文字颜色 1" xfId="23" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="强调文字颜色 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="强调文字颜色 3" xfId="31" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="强调文字颜色 4" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="强调文字颜色 5" xfId="38" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="强调文字颜色 6" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="适中" xfId="20" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="输出" xfId="22" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="输入" xfId="21" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="注释" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -915,7 +825,7 @@
               <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="false"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -928,7 +838,7 @@
               <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="false"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -958,7 +868,7 @@
                 <a:schemeClr val="phClr"/>
               </a:gs>
             </a:gsLst>
-            <a:lin ang="2700000" scaled="true"/>
+            <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
@@ -967,7 +877,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
               <a:schemeClr val="phClr">
                 <a:alpha val="60000"/>
               </a:schemeClr>
@@ -976,12 +886,12 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="false"/>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -999,7 +909,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1024,143 +934,112 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
-  <dimension ref="B11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.625"/>
+    <col min="1" max="1" width="30.58203125"/>
     <col min="2" max="2" width="80.75"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3"/>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15">
-      <c r="A2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>8</v>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>10</v>
+      <c r="B5" s="5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>14</v>
+    <row r="7" spans="1:2" ht="30">
+      <c r="B7" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>18</v>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>22</v>
+    <row r="11" spans="1:2" ht="45">
+      <c r="B11" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511806" footer="0.511806"/>
+  <phoneticPr fontId="22" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180599999999998" footer="0.51180599999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="false"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
-  <sheetProtection/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511806" footer="0.511806"/>
+  <phoneticPr fontId="22" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180599999999998" footer="0.51180599999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="false"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
-  <sheetProtection/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511806" footer="0.511806"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="false"/>
+  <phoneticPr fontId="22" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180599999999998" footer="0.51180599999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>